--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>10.81</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>9.470000000000001</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>9.41</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>9</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>8.800000000000001</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>8.6</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>8.1</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>7.95</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>7.85</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>6.54</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>6.53</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>6.35</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>5.75</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>5.66</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>4.89</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>4.4</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>4.25</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>3.96</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>3.74</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>3.74</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>3.71</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>3.62</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>3.62</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>3.52</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>3.44</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>3.36</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>3.36</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>3.23</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>3.12</v>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -772,9 +680,6 @@
       </c>
       <c r="B31">
         <v>1.94</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>10.81</v>
       </c>
+      <c r="C2">
+        <v>11.62</v>
+      </c>
+      <c r="D2">
+        <v>-0.8099999999999987</v>
+      </c>
+      <c r="E2">
+        <v>-6.970740103270212</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>9.470000000000001</v>
       </c>
+      <c r="C3">
+        <v>9.5</v>
+      </c>
+      <c r="D3">
+        <v>-0.02999999999999936</v>
+      </c>
+      <c r="E3">
+        <v>-0.3157894736842026</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>9.41</v>
       </c>
+      <c r="C4">
+        <v>9.65</v>
+      </c>
+      <c r="D4">
+        <v>-0.2400000000000002</v>
+      </c>
+      <c r="E4">
+        <v>-2.487046632124357</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>9</v>
       </c>
+      <c r="C5">
+        <v>9.35</v>
+      </c>
+      <c r="D5">
+        <v>-0.3499999999999996</v>
+      </c>
+      <c r="E5">
+        <v>-3.743315508021383</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>8.800000000000001</v>
       </c>
+      <c r="C6">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D6">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="E6">
+        <v>1.149425287356332</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>8.6</v>
       </c>
+      <c r="C7">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="D7">
+        <v>-0.2699999999999996</v>
+      </c>
+      <c r="E7">
+        <v>-3.043968432919952</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>8.1</v>
       </c>
+      <c r="C8">
+        <v>8.25</v>
+      </c>
+      <c r="D8">
+        <v>-0.1500000000000004</v>
+      </c>
+      <c r="E8">
+        <v>-1.818181818181819</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +524,15 @@
       <c r="B9">
         <v>7.95</v>
       </c>
+      <c r="C9">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="D9">
+        <v>-0.3299999999999992</v>
+      </c>
+      <c r="E9">
+        <v>-3.985507246376807</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +543,15 @@
       <c r="B10">
         <v>7.85</v>
       </c>
+      <c r="C10">
+        <v>6.87</v>
+      </c>
+      <c r="D10">
+        <v>0.9799999999999995</v>
+      </c>
+      <c r="E10">
+        <v>14.26491994177583</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -481,6 +562,15 @@
       <c r="B11">
         <v>6.54</v>
       </c>
+      <c r="C11">
+        <v>6.61</v>
+      </c>
+      <c r="D11">
+        <v>-0.07000000000000028</v>
+      </c>
+      <c r="E11">
+        <v>-1.059001512859303</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -491,6 +581,15 @@
       <c r="B12">
         <v>6.53</v>
       </c>
+      <c r="C12">
+        <v>6.65</v>
+      </c>
+      <c r="D12">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="E12">
+        <v>-1.804511278195486</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -501,6 +600,15 @@
       <c r="B13">
         <v>6.35</v>
       </c>
+      <c r="C13">
+        <v>6.93</v>
+      </c>
+      <c r="D13">
+        <v>-0.5800000000000001</v>
+      </c>
+      <c r="E13">
+        <v>-8.369408369408371</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -511,6 +619,15 @@
       <c r="B14">
         <v>5.75</v>
       </c>
+      <c r="C14">
+        <v>4.55</v>
+      </c>
+      <c r="D14">
+        <v>1.2</v>
+      </c>
+      <c r="E14">
+        <v>26.37362637362637</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -521,165 +638,337 @@
       <c r="B15">
         <v>5.66</v>
       </c>
+      <c r="C15">
+        <v>5.81</v>
+      </c>
+      <c r="D15">
+        <v>-0.1499999999999995</v>
+      </c>
+      <c r="E15">
+        <v>-2.581755593803781</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B16">
-        <v>4.89</v>
+        <v>5.14</v>
+      </c>
+      <c r="C16">
+        <v>5.24</v>
+      </c>
+      <c r="D16">
+        <v>-0.1000000000000005</v>
+      </c>
+      <c r="E16">
+        <v>-1.908396946564894</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="B17">
-        <v>4.4</v>
+        <v>4.89</v>
+      </c>
+      <c r="C17">
+        <v>5.2</v>
+      </c>
+      <c r="D17">
+        <v>-0.3100000000000005</v>
+      </c>
+      <c r="E17">
+        <v>-5.961538461538474</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="B18">
-        <v>4.25</v>
+        <v>4.4</v>
+      </c>
+      <c r="C18">
+        <v>5.22</v>
+      </c>
+      <c r="D18">
+        <v>-0.8199999999999994</v>
+      </c>
+      <c r="E18">
+        <v>-15.70881226053639</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="B19">
-        <v>3.96</v>
+        <v>4.25</v>
+      </c>
+      <c r="C19">
+        <v>5.25</v>
+      </c>
+      <c r="D19">
+        <v>-1</v>
+      </c>
+      <c r="E19">
+        <v>-19.04761904761905</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="B20">
-        <v>3.74</v>
+        <v>3.96</v>
+      </c>
+      <c r="C20">
+        <v>3.9</v>
+      </c>
+      <c r="D20">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="E20">
+        <v>1.538461538461533</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="B21">
         <v>3.74</v>
       </c>
+      <c r="C21">
+        <v>3.49</v>
+      </c>
+      <c r="D21">
+        <v>0.25</v>
+      </c>
+      <c r="E21">
+        <v>7.163323782234965</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="B22">
-        <v>3.71</v>
+        <v>3.74</v>
+      </c>
+      <c r="C22">
+        <v>3.89</v>
+      </c>
+      <c r="D22">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="E22">
+        <v>-3.856041131105392</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="B23">
-        <v>3.62</v>
+        <v>3.71</v>
+      </c>
+      <c r="C23">
+        <v>3.98</v>
+      </c>
+      <c r="D23">
+        <v>-0.27</v>
+      </c>
+      <c r="E23">
+        <v>-6.783919597989952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="B24">
         <v>3.62</v>
       </c>
+      <c r="C24">
+        <v>3.44</v>
+      </c>
+      <c r="D24">
+        <v>0.1800000000000002</v>
+      </c>
+      <c r="E24">
+        <v>5.232558139534893</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="B25">
-        <v>3.52</v>
+        <v>3.62</v>
+      </c>
+      <c r="C25">
+        <v>4.3</v>
+      </c>
+      <c r="D25">
+        <v>-0.6799999999999997</v>
+      </c>
+      <c r="E25">
+        <v>-15.81395348837209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="B26">
-        <v>3.44</v>
+        <v>3.52</v>
+      </c>
+      <c r="C26">
+        <v>3.73</v>
+      </c>
+      <c r="D26">
+        <v>-0.21</v>
+      </c>
+      <c r="E26">
+        <v>-5.630026809651478</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="B27">
-        <v>3.36</v>
+        <v>3.44</v>
+      </c>
+      <c r="C27">
+        <v>3.71</v>
+      </c>
+      <c r="D27">
+        <v>-0.27</v>
+      </c>
+      <c r="E27">
+        <v>-7.277628032345018</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="B28">
         <v>3.36</v>
       </c>
+      <c r="C28">
+        <v>3.06</v>
+      </c>
+      <c r="D28">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="E28">
+        <v>9.803921568627437</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="B29">
-        <v>3.23</v>
+        <v>3.36</v>
+      </c>
+      <c r="C29">
+        <v>3.18</v>
+      </c>
+      <c r="D29">
+        <v>0.1799999999999997</v>
+      </c>
+      <c r="E29">
+        <v>5.660377358490565</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="B30">
+        <v>3.23</v>
+      </c>
+      <c r="C30">
         <v>3.12</v>
+      </c>
+      <c r="D30">
+        <v>0.1099999999999999</v>
+      </c>
+      <c r="E30">
+        <v>3.525641025641013</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>3.12</v>
+      </c>
+      <c r="C31">
+        <v>3.12</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Puqueldón</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>1.94</v>
+      </c>
+      <c r="C32">
+        <v>1.93</v>
+      </c>
+      <c r="D32">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="E32">
+        <v>0.5181347150259086</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_lagos.xlsx
@@ -978,7 +978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -987,310 +987,215 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ancud</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>6.53</v>
+          <t>San Pablo</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Calbuco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>3.71</v>
+          <t>Puqueldón</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Castro</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>3.52</v>
+          <t>Fresia</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chaitén</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>3.44</v>
+          <t>Llanquihue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chonchi</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>3.74</v>
+          <t>Osorno</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cochamó</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>3.96</v>
+          <t>Purranque</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>3.23</v>
+          <t>Puyehue</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>3.62</v>
+          <t>Cochamó</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fresia</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>10.81</v>
+          <t>Ancud</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Frutillar</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>8.1</v>
+          <t>Quellón</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>4.25</v>
+          <t>Queilén</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>3.62</v>
+          <t>Chonchi</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>5.66</v>
+          <t>Puerto Montt</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>9.41</v>
+          <t>Río Negro</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maullín</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>6.35</v>
+          <t>Castro</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Osorno</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>6.54</v>
+          <t>Dalcahue</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Palena</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>4.4</v>
+          <t>Quemchi</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>3.74</v>
+          <t>San Juan de la Costa</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>9.470000000000001</v>
+          <t>Calbuco</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>4.89</v>
+          <t>Chaitén</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>1.94</v>
+          <t>Los Muermos</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Purranque</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>7.95</v>
+          <t>Maullín</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Puyehue</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>8.800000000000001</v>
+          <t>Quinchao</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Queilén</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>3.36</v>
+          <t>Curaco de Vélez</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quellón</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>3.36</v>
+          <t>Puerto Octay</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quemchi</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>5.75</v>
+          <t>Frutillar</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quinchao</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>3.12</v>
+          <t>Puerto Varas</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Río Negro</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>9</v>
+          <t>Hualaihué</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>7.85</v>
+          <t>Palena</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Pablo</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>8.6</v>
+          <t>Futaleufú</t>
+        </is>
       </c>
     </row>
   </sheetData>
